--- a/output/pdf_financials_xlsx/CANS.xlsx
+++ b/output/pdf_financials_xlsx/CANS.xlsx
@@ -3653,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>3.921</v>
@@ -9590,7 +9590,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -10279,7 +10283,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CANS.xlsx
+++ b/output/pdf_financials_xlsx/CANS.xlsx
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000671</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.057918</v>
+        <v>-0.058238</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.452744</v>
+        <v>-1.453415</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.000427</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.057918</v>
+        <v>-0.058238</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.452744</v>
+        <v>-1.453415</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.000427</v>
@@ -1610,25 +1610,25 @@
         <v>0.227459</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.08980399999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.54909</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.498083</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="35">
@@ -1678,25 +1678,25 @@
         <v>0.227459</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.08980399999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.54909</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.498083</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="37">
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.043</v>
+        <v>1.1</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.966</v>
+        <v>1.316</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.931</v>
+        <v>1.677</v>
       </c>
     </row>
     <row r="49">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E380" s="5" t="n">

--- a/output/pdf_financials_xlsx/CANS.xlsx
+++ b/output/pdf_financials_xlsx/CANS.xlsx
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.017281</v>
+        <v>0.048781</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.08516</v>
+        <v>0.56941</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.000427</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.01741</v>
+        <v>0.04891</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.086107</v>
+        <v>0.570357</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.000427</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>0.919743</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>0.12574</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.065456</v>
+        <v>0.985199</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.227459</v>
+        <v>0.353199</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.08980399999999999</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.92827</v>
+        <v>0.008527</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.17871</v>
+        <v>0.05297</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.010877</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.006761</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.017071</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.047474</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.000231</v>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.019421</v>
+        <v>0.00235</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.047515</v>
+        <v>4.1e-05</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>7.142525</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>7.992525</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>0.105</v>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.183383</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.183383</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -10781,7 +10781,11 @@
           <t>Due from related parties – Note 7</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
         <v>0.008527</v>
       </c>
@@ -10840,7 +10844,11 @@
           <t>Marketable Securities – Note 8</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.919743</v>
       </c>
@@ -10899,7 +10907,11 @@
           <t>Prepaid and Deposits – Note 12</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -11080,7 +11092,11 @@
           <t>Accounts payable and accrued liabilities – Note 6 &amp; 7 $</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>0.017071</v>
       </c>
@@ -11139,7 +11155,11 @@
           <t>Due to related parties – Note 7</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>0.00235</v>
       </c>
@@ -11198,7 +11218,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
         <v>7.142525</v>
       </c>
@@ -11318,7 +11342,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>0.183383</v>
       </c>
@@ -27662,7 +27690,11 @@
           <t>Consulting and management fees – Note 7</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E369" s="5" t="n">
         <v>0.0315</v>
       </c>

--- a/output/pdf_financials_xlsx/CANS.xlsx
+++ b/output/pdf_financials_xlsx/CANS.xlsx
@@ -1823,16 +1823,16 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.832</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>1.076</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="41">
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3.826</v>
+        <v>4.658</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>5.138</v>
+        <v>5.358</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>11.095</v>
+        <v>12.171</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>8.547000000000001</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="42">
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.316</v>
+        <v>0.24</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.677</v>
+        <v>1.414</v>
       </c>
     </row>
     <row r="49">
@@ -2885,16 +2885,16 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>2.404</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>8.167999999999999</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>6.212</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>4.945</v>
       </c>
     </row>
     <row r="71">
@@ -2919,16 +2919,16 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>27.043</v>
+        <v>29.447</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>7.422</v>
+        <v>15.59</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>54.248</v>
+        <v>60.46</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>85.40600000000001</v>
+        <v>90.351</v>
       </c>
     </row>
     <row r="72">
@@ -3058,13 +3058,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.107</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.092</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>3.649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3239,16 +3239,16 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1.121127911728647</v>
+        <v>1.219370657948508</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>-4.091682879377432</v>
+        <v>-5.084873540856031</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-2.266143461288224</v>
+        <v>-2.518745933636955</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>-1.190044253868778</v>
+        <v>-1.258005552348753</v>
       </c>
     </row>
     <row r="81">
@@ -4282,16 +4282,16 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-3.211</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.398</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.208</v>
       </c>
     </row>
     <row r="112">
@@ -5086,16 +5086,16 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-3.211</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.398</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.208</v>
       </c>
     </row>
     <row r="135">
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-16.015</v>
+        <v>-19.226</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.964</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-17.959</v>
+        <v>-20.429</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.497999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,11 @@
           <t>Current portion of lease obligations 11</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -6567,7 +6571,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -7301,7 +7309,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -7423,7 +7435,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -8667,7 +8683,11 @@
           <t>Current portion of lease obligations 14</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12973,7 +12993,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -14248,7 +14272,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -18678,7 +18706,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -23012,7 +23044,11 @@
           <t>Deferred income tax recovery 17</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
